--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,1008 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133510227</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>724759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7279939</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133519377</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92092</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>724653</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7280001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133553426</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>724714</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7279958</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133515710</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>725010</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7280123</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133511812</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>724746</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7280090</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133511351</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>724713</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7280078</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fodersök</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133554219</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>725010</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7280123</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ullticka med Ulltickporing</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133520247</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>724714</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7279958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tallticka med bohål under</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133517404</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storholmen, Storholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>725010</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7280123</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133515710</v>
+        <v>133511812</v>
       </c>
       <c r="B8" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725010</v>
+        <v>724746</v>
       </c>
       <c r="R8" t="n">
-        <v>7280123</v>
+        <v>7280090</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,32 +1463,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133511812</v>
+        <v>133515710</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724746</v>
+        <v>725010</v>
       </c>
       <c r="R9" t="n">
-        <v>7280090</v>
+        <v>7280123</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Heike Kontermann</t>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>133529612</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>133510227</v>
       </c>
       <c r="B5" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>133519377</v>
       </c>
       <c r="B6" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>133511812</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>133515710</v>
       </c>
       <c r="B9" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>133554219</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>133520247</v>
       </c>
       <c r="B12" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>133517404</v>
       </c>
       <c r="B13" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>133529612</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>133519377</v>
       </c>
       <c r="B6" t="n">
-        <v>92094</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>133515710</v>
       </c>
       <c r="B9" t="n">
-        <v>92292</v>
+        <v>92300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>133554219</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Heike Kontermann</t>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>133520247</v>
       </c>
       <c r="B12" t="n">
-        <v>91941</v>
+        <v>91949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133529617</v>
+        <v>133554219</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storholmen Östra Kikkejaure, Pi lm</t>
+          <t>Storholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725007</v>
+        <v>725010</v>
       </c>
       <c r="R2" t="n">
         <v>7280123</v>
       </c>
       <c r="S2" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,14 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ullticka med Ulltickporing</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,82 +762,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Heike Kontermann</t>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133529613</v>
+        <v>133519377</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>92153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storholmen Östra Kikkejaure, Pi lm</t>
+          <t>Storholmen, Storholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724739</v>
+        <v>724653</v>
       </c>
       <c r="R3" t="n">
-        <v>7279984</v>
+        <v>7280001</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,28 +873,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Heike Kontermann</t>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133529612</v>
+        <v>133515710</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>92318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,37 +903,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storholmen Östra Kikkejaure, Pi lm</t>
+          <t>Storholmen, Storholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724838</v>
+        <v>725010</v>
       </c>
       <c r="R4" t="n">
-        <v>7279844</v>
+        <v>7280123</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertal rosetter</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,28 +984,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Heike Kontermann</t>
+          <t>Heike Kontermann, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133510227</v>
+        <v>133529618</v>
       </c>
       <c r="B5" t="n">
-        <v>79978</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,40 +1014,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Pi lm</t>
+          <t>Storholmen Östra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724759</v>
+        <v>724840</v>
       </c>
       <c r="R5" t="n">
-        <v>7279939</v>
+        <v>7280134</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,51 +1092,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133519377</v>
+        <v>133520247</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724653</v>
+        <v>724714</v>
       </c>
       <c r="R6" t="n">
-        <v>7280001</v>
+        <v>7279958</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1209,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tallticka med bohål under</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,56 +1226,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133553426</v>
+        <v>133511812</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storholmen, Pi lm</t>
+          <t>Storholmen, Storholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724714</v>
+        <v>724746</v>
       </c>
       <c r="R7" t="n">
-        <v>7279958</v>
+        <v>7280090</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,17 +1297,28 @@
           <t>2026-05-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133511812</v>
+        <v>133510227</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724746</v>
+        <v>724759</v>
       </c>
       <c r="R8" t="n">
-        <v>7280090</v>
+        <v>7279939</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133515710</v>
+        <v>133517404</v>
       </c>
       <c r="B9" t="n">
-        <v>92304</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,7 +1492,7 @@
         <v>7280123</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1566,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1694,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133554219</v>
+        <v>133553426</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,26 +1690,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725010</v>
+        <v>724714</v>
       </c>
       <c r="R11" t="n">
-        <v>7280123</v>
+        <v>7279958</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,18 +1760,12 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ullticka med Ulltickporing</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,51 +1784,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133520247</v>
+        <v>133529617</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Pi lm</t>
+          <t>Storholmen Östra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724714</v>
+        <v>725007</v>
       </c>
       <c r="R12" t="n">
-        <v>7279958</v>
+        <v>7280123</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,12 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tallticka med bohål under</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,29 +1881,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133517404</v>
+        <v>133529613</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,40 +1910,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Pi lm</t>
+          <t>Storholmen Östra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725010</v>
+        <v>724739</v>
       </c>
       <c r="R13" t="n">
-        <v>7280123</v>
+        <v>7279984</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,22 +2004,133 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133529612</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storholmen Östra Kikkejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>724838</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7279844</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flertal rosetter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10242-2026 artfynd.xlsx
+++ b/artfynd/A 10242-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133554219</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133519377</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133529618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133520247</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133511812</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133510227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133517404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133511351</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133553426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133529617</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133529613</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,8 +2196,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133529612</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>